--- a/dashboard/leitura/Parcial_Americana.xlsx
+++ b/dashboard/leitura/Parcial_Americana.xlsx
@@ -473,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -532,17 +532,17 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>CICERO ADRIANO SABINO</t>
+          <t>FRANCISCO ANILTON LIMA SILVA</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
@@ -551,17 +551,17 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>JEFERSON MENDES MORENO</t>
+          <t>JONATHAN A TOLEDO</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13</v>
+        <v>282</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13</v>
+        <v>282</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
@@ -570,533 +570,533 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>JONATHAN A TOLEDO</t>
+          <t>TIAGO MEIRELES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>282</v>
+        <v>90</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>282</v>
+        <v>90</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>TIAGO MEIRELES DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CICERO ADRIANO SABINO</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>13.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ALEX CAVALCANTE DUARTE</t>
+          <t>WILLYTON MOREIRA DO NASCIMENTO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>158</v>
+        <v>448</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1</v>
+        <v>276</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.63</v>
+        <v>61.61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>WILLYTON MOREIRA DO NASCIMENTO</t>
+          <t>JOAO MARCOS CHRISOSTOMO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>448</v>
+        <v>789</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>89</v>
+        <v>653</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>359</v>
+        <v>136</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>19.87</v>
+        <v>82.76000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ROGERIO FERREIRA RODRIGUES</t>
+          <t>JEAN ANTONIO ARGENTIN TORRES</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>9</v>
+        <v>483</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2</v>
+        <v>421</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>22.22</v>
+        <v>87.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CLÉCIO REIS DA SILVA.</t>
+          <t>EDUARDO DE ABREU BARBOSA</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>8</v>
+        <v>910</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>40</v>
+        <v>91.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>JEAN ANTONIO ARGENTIN TORRES</t>
+          <t>EUGENIO RESERVA</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>554</v>
+        <v>655</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>227</v>
+        <v>597</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>327</v>
+        <v>58</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>40.97</v>
+        <v>91.15000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>JOAO MARCOS CHRISOSTOMO</t>
+          <t>WILTON DO CARMO MORIS ARAUJO</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>789</v>
+        <v>472</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>371</v>
+        <v>432</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>418</v>
+        <v>40</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>47.02</v>
+        <v>91.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DAVID FERNANDO LUIZ</t>
+          <t>CICERO AVERALDO DA SILVA NOVO</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>636</v>
+        <v>1314</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>331</v>
+        <v>1286</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>305</v>
+        <v>28</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>52.04</v>
+        <v>97.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EUGENIO RESERVA</t>
+          <t>MAYCON SOARES PROVISÓRIO</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>655</v>
+        <v>850</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>351</v>
+        <v>841</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>304</v>
+        <v>9</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>53.59</v>
+        <v>98.94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CICERO AVERALDO DA SILVA NOVO</t>
+          <t>CLAITON ALVES DAS SILVA NOVO</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1314</v>
+        <v>344</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>733</v>
+        <v>342</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>581</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>55.78</v>
+        <v>99.42</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>EDSON CUSTODIO DE MELLO</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>839</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>839</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>ARTHUR RIBEIRO DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>793</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>793</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>HENRY JOSE DA COSTA</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>593</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>593</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>CLÉCIO REIS DA SILVA.</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>DAVID FERNANDO LUIZ</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>636</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>636</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>JEFERSON MENDES MORENO</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>JOSE WANDERSON SANTOS DE OLIVE</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>847</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>847</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>JOSÉ FERNANDES BENEDICTO</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>816</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>816</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>LUCIANA RIBEIRO ROMPATO</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>598</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>598</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>JOAQUIM ESTEVES RAMOS NOVO</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>731</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>731</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>LUCIANO ISLER</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B26" s="6" t="n">
         <v>552</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>332</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>220</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>60.14</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>EDUARDO DE ABREU BARBOSA</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>999</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>614</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>385</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>61.46</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="C26" s="6" t="n">
+        <v>552</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>MARCELO BANDEIRA</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>MARCIO DOS REIS ALVARENGA</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B28" s="6" t="n">
         <v>1110</v>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>709</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>401</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>63.87</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>JOAQUIM ESTEVES RAMOS NOVO</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>731</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>474</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>64.84</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>VALDIRLEI PASCHOALIN</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>781</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>507</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>274</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>64.92</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>ARTHUR RIBEIRO DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>793</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>543</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>250</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>68.47</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>WILTON DO CARMO MORIS ARAUJO</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>472</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>327</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>145</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>69.28</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>HENRY JOSE DA COSTA</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>593</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>426</v>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>167</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>71.84</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="C28" s="6" t="n">
+        <v>1110</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>NELSON LUIZ CARDOZO</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>844</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>844</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>NEUMARA ALMEIDA DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>644</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>644</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>ADISON LOPES LIMA SILVA</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B31" s="6" t="n">
         <v>701</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>514</v>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>187</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>73.31999999999999</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>NELSON LUIZ CARDOZO</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>844</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>625</v>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>219</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>74.05</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>JOSE WANDERSON SANTOS DE OLIVE</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>847</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>698</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>149</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>82.41</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>VAGNER DE SOUSA SANTOS</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>385</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>319</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>82.86</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>EDSON CUSTODIO DE MELLO</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>839</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>711</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>84.73999999999999</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>MAYCON SOARES PROVISÓRIO</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>850</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>735</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>86.47</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>ROBSON PERECINI SANTOS COSTA</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>393</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>356</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>90.59</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>NEUMARA ALMEIDA DOS SANTOS</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>644</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>619</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>96.12</v>
+      <c r="C31" s="6" t="n">
+        <v>701</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>JOSÉ FERNANDES BENEDICTO</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>815</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>806</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>98.90000000000001</v>
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>ALEX CAVALCANTE DUARTE</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>158</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>158</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -1121,14 +1121,14 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>SERGIO DA SILVA CORAGEM</t>
+          <t>ROGERIO FERREIRA RODRIGUES</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>0</v>
@@ -1140,14 +1140,14 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>RENAILTON SANTIAGO DE OLIVEIRA</t>
+          <t>ROBSON PERECINI SANTOS COSTA</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>0</v>
@@ -1159,14 +1159,14 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>LUCIANA RIBEIRO ROMPATO</t>
+          <t>RENAILTON SANTIAGO DE OLIVEIRA</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>598</v>
+        <v>367</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>598</v>
+        <v>367</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>0</v>
@@ -1178,14 +1178,14 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>MARCELO BANDEIRA</t>
+          <t>SERGIO DA SILVA CORAGEM</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>0</v>
@@ -1197,19 +1197,38 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>CLAITON ALVES DAS SILVA NOVO</t>
+          <t>VALDIRLEI PASCHOALIN</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>342</v>
+        <v>781</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>342</v>
+        <v>781</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E38" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>VAGNER DE SOUSA SANTOS</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>456</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>456</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="7" t="n">
         <v>100</v>
       </c>
     </row>

--- a/dashboard/leitura/Parcial_Americana.xlsx
+++ b/dashboard/leitura/Parcial_Americana.xlsx
@@ -634,13 +634,13 @@
         <v>789</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>653</v>
+        <v>684</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>82.76000000000001</v>
+        <v>86.69</v>
       </c>
     </row>
     <row r="9">
@@ -665,58 +665,58 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>EDUARDO DE ABREU BARBOSA</t>
+          <t>EUGENIO RESERVA</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>999</v>
+        <v>655</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>910</v>
+        <v>597</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>91.09</v>
+        <v>91.15000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EUGENIO RESERVA</t>
+          <t>WILTON DO CARMO MORIS ARAUJO</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>655</v>
+        <v>472</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>597</v>
+        <v>432</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>91.15000000000001</v>
+        <v>91.53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>WILTON DO CARMO MORIS ARAUJO</t>
+          <t>EDUARDO DE ABREU BARBOSA</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>472</v>
+        <v>999</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>432</v>
+        <v>942</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>91.53</v>
+        <v>94.29000000000001</v>
       </c>
     </row>
     <row r="13">

--- a/dashboard/leitura/Parcial_Americana.xlsx
+++ b/dashboard/leitura/Parcial_Americana.xlsx
@@ -568,41 +568,41 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>TIAGO MEIRELES DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CICERO ADRIANO SABINO</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>13.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CICERO ADRIANO SABINO</t>
+          <t>TIAGO MEIRELES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>13.33</v>
+        <v>14.44</v>
       </c>
     </row>
     <row r="7">
@@ -615,13 +615,13 @@
         <v>448</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>61.61</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="8">
@@ -646,58 +646,58 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>JEAN ANTONIO ARGENTIN TORRES</t>
+          <t>EUGENIO RESERVA</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>483</v>
+        <v>655</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>421</v>
+        <v>597</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>87.16</v>
+        <v>91.15000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>EUGENIO RESERVA</t>
+          <t>WILTON DO CARMO MORIS ARAUJO</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>655</v>
+        <v>472</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>597</v>
+        <v>439</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>91.15000000000001</v>
+        <v>93.01000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>WILTON DO CARMO MORIS ARAUJO</t>
+          <t>JEAN ANTONIO ARGENTIN TORRES</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>91.53</v>
+        <v>94.41</v>
       </c>
     </row>
     <row r="12">
@@ -710,13 +710,13 @@
         <v>999</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>942</v>
+        <v>974</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>94.29000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="13">
